--- a/src/test/resources/Exceldata/Data.xlsx
+++ b/src/test/resources/Exceldata/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eclipse-workspace\RedBus\src\test\resources\Exceldata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024D0DF7-436D-4A29-8D80-58B14E7E9363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69BCD3F-5338-4155-9E2E-991906FD43F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4212" yWindow="1080" windowWidth="11868" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HomePage" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>Chennai</t>
   </si>
   <si>
-    <t>Trichy</t>
-  </si>
-  <si>
     <t>BannerFilter</t>
   </si>
   <si>
@@ -72,15 +69,6 @@
     <t>Free date change</t>
   </si>
   <si>
-    <t>YBM Travels(BLM)</t>
-  </si>
-  <si>
-    <t>REDHILLS YBM YARD</t>
-  </si>
-  <si>
-    <t>Central Bus Stand, Tiruchirapalli</t>
-  </si>
-  <si>
     <t>Phone number</t>
   </si>
   <si>
@@ -130,6 +118,18 @@
   </si>
   <si>
     <t>June 30, 2026</t>
+  </si>
+  <si>
+    <t>Salem</t>
+  </si>
+  <si>
+    <t>MRS Transport</t>
+  </si>
+  <si>
+    <t>KOYEMBEDU</t>
+  </si>
+  <si>
+    <t>KALLAKURICHI</t>
   </si>
 </sst>
 </file>
@@ -493,10 +493,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -521,60 +521,60 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -594,13 +594,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -608,10 +608,10 @@
         <v>9123456720</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -634,16 +634,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -651,7 +651,7 @@
         <v>1234567801234560</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1">
         <v>1030</v>
